--- a/tests/workbooktests/workbooks/test_calibrationhelpers.xlsx
+++ b/tests/workbooktests/workbooks/test_calibrationhelpers.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B723D96A-22E1-4A3B-94CC-5220F3F2A5D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE3A3994-B456-4387-B692-AD9BD66A8F87}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3645" yWindow="-19185" windowWidth="30690" windowHeight="16530" xr2:uid="{F8183AC6-1ED6-4E47-A659-19168C9694C8}"/>
   </bookViews>
@@ -22,17 +22,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -41,14 +30,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -222,7 +211,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -284,8 +273,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Prozent" xfId="1" builtinId="5"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -618,16 +607,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66B0E03E-5553-43AC-8BBA-E17D5646A164}">
   <dimension ref="A1:E30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="37.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.6640625" customWidth="1"/>
+    <col min="1" max="1" width="37.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.625" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="19.44140625" customWidth="1"/>
-    <col min="5" max="5" width="19.109375" customWidth="1"/>
+    <col min="4" max="4" width="19.5" customWidth="1"/>
+    <col min="5" max="5" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -635,34 +624,34 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B2" ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="3">
+        <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="e" cm="1">
-        <f t="array" aca="1" ref="B4" ca="1">_xll.qlFlatForward(B2,0.03)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B4" t="str">
+        <f>_xll.qlFlatForward(B2,0.03,"actual365fixed")</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlSwaptionHelper!R4C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" t="e" cm="1">
-        <f t="array" aca="1" ref="B5" ca="1">_xll.qlFlatForward(B2,0.02)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B5" t="str">
+        <f>_xll.qlFlatForward(B2,0.02,"actual365fixed")</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlSwaptionHelper!R5C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="B7" t="s">
         <v>0</v>
       </c>
@@ -676,7 +665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -686,16 +675,16 @@
       <c r="C8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="8" t="e">
-        <f ca="1">B2+365</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E8" s="8" t="e">
-        <f ca="1">B2+365</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D8" s="8">
+        <f>B2+365</f>
+        <v>46539</v>
+      </c>
+      <c r="E8" s="8">
+        <f>B2+365</f>
+        <v>46539</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -708,12 +697,12 @@
       <c r="D9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="8" t="e">
-        <f ca="1">E8+730</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E9" s="8">
+        <f>E8+730</f>
+        <v>47269</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -730,28 +719,28 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B11" ca="1">_xll.qlEuribor("6M",$B$4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C11" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="C11" ca="1">_xll.qlEuribor("6M",B4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D11" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="D11" ca="1">_xll.qlEuribor("6M",$B$4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E11" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="E11" ca="1">_xll.qlEuribor("6M",$B$4)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="4" t="str">
+        <f t="array" ref="B11">_xll.qlEuribor("6M",$B$4)</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlSwaptionHelper!R11C2Euribor,A</v>
+      </c>
+      <c r="C11" s="4" t="str">
+        <f t="array" ref="C11">_xll.qlEuribor("6M",B4)</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlSwaptionHelper!R11C3Euribor,A</v>
+      </c>
+      <c r="D11" s="4" t="str">
+        <f t="array" ref="D11">_xll.qlEuribor("6M",$B$4)</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlSwaptionHelper!R11C4Euribor,A</v>
+      </c>
+      <c r="E11" s="4" t="str">
+        <f t="array" ref="E11">_xll.qlEuribor("6M",$B$4)</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlSwaptionHelper!R11C5Euribor,A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -768,7 +757,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -785,7 +774,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -802,28 +791,28 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="4" t="e">
-        <f ca="1">$B$5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C15" s="4" t="e">
-        <f ca="1">B5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D15" s="4" t="e">
-        <f ca="1">$B$5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E15" s="4" t="e">
-        <f ca="1">$B$5</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="4" t="str">
+        <f>$B$5</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlSwaptionHelper!R5C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C15" s="4" t="str">
+        <f>B5</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlSwaptionHelper!R5C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="D15" s="4" t="str">
+        <f>$B$5</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlSwaptionHelper!R5C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="E15" s="4" t="str">
+        <f>$B$5</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlSwaptionHelper!R5C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -834,7 +823,7 @@
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -845,7 +834,7 @@
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -856,7 +845,7 @@
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -867,7 +856,7 @@
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -878,7 +867,7 @@
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -889,7 +878,7 @@
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -900,127 +889,127 @@
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B24" t="e" cm="1">
-        <f t="array" aca="1" ref="B24" ca="1">_xll.qlSwaptionHelper(B8,B9,B10,B11,B12,B13,B14,B15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C24" t="e" cm="1">
-        <f t="array" aca="1" ref="C24" ca="1">_xll.qlSwaptionHelper(C8,C9,C10,C11,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D24" t="e" cm="1">
-        <f t="array" aca="1" ref="D24" ca="1">_xll.qlSwaptionHelper(D8,D9,D10,D11,D12,D13,D14,D15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E24" t="e" cm="1">
-        <f t="array" aca="1" ref="E24" ca="1">_xll.qlSwaptionHelper(E8,E9,E10,E11,E12,E13,E14,E15)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5">
+      <c r="B24" t="str">
+        <f t="array" ref="B24">_xll.qlSwaptionHelper(B8,B9,B10,B11,B12,B13,B14,B15)</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlSwaptionHelper!R24C2SwaptionHelper,A</v>
+      </c>
+      <c r="C24" t="str">
+        <f t="array" ref="C24">_xll.qlSwaptionHelper(C8,C9,C10,C11,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22)</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlSwaptionHelper!R24C3SwaptionHelper,A</v>
+      </c>
+      <c r="D24" t="str">
+        <f t="array" ref="D24">_xll.qlSwaptionHelper(D8,D9,D10,D11,D12,D13,D14,D15)</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlSwaptionHelper!R24C4SwaptionHelper,A</v>
+      </c>
+      <c r="E24" t="str">
+        <f t="array" ref="E24">_xll.qlSwaptionHelper(E8,E9,E10,E11,E12,E13,E14,E15)</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlSwaptionHelper!R24C5SwaptionHelper,A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>29</v>
       </c>
-      <c r="B26" t="e" cm="1">
-        <f t="array" aca="1" ref="B26" ca="1">_xll.qlBlackCalibrationHelperMarketValue(B24)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C26" t="e" cm="1">
-        <f t="array" aca="1" ref="C26" ca="1">_xll.qlBlackCalibrationHelperMarketValue(C24)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D26" t="e" cm="1">
-        <f t="array" aca="1" ref="D26" ca="1">_xll.qlBlackCalibrationHelperMarketValue(D24)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E26" t="e" cm="1">
-        <f t="array" aca="1" ref="E26" ca="1">_xll.qlBlackCalibrationHelperMarketValue(E24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B26">
+        <f t="array" ref="B26">_xll.qlBlackCalibrationHelperMarketValue(B24)</f>
+        <v>9.1854188200250798E-3</v>
+      </c>
+      <c r="C26">
+        <f t="array" ref="C26">_xll.qlBlackCalibrationHelperMarketValue(C24)</f>
+        <v>0.5687196556581241</v>
+      </c>
+      <c r="D26">
+        <f t="array" ref="D26">_xll.qlBlackCalibrationHelperMarketValue(D24)</f>
+        <v>9.1854188200250798E-3</v>
+      </c>
+      <c r="E26">
+        <f t="array" ref="E26">_xll.qlBlackCalibrationHelperMarketValue(E24)</f>
+        <v>9.1360994073147565E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B27" ca="1">_xll.qlBlackCalibrationHelperImpliedVolatility(B24,B26)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C27" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="C27" ca="1">_xll.qlBlackCalibrationHelperImpliedVolatility(C24,C26)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D27" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="D27" ca="1">_xll.qlBlackCalibrationHelperImpliedVolatility(D24,D26)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E27" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="E27" ca="1">_xll.qlBlackCalibrationHelperImpliedVolatility(E24,E26)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B27" s="1">
+        <f t="array" ref="B27">_xll.qlBlackCalibrationHelperImpliedVolatility(B24,B26)</f>
+        <v>0.4</v>
+      </c>
+      <c r="C27" s="2">
+        <f t="array" ref="C27">_xll.qlBlackCalibrationHelperImpliedVolatility(C24,C26)</f>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="D27" s="2">
+        <f t="array" ref="D27">_xll.qlBlackCalibrationHelperImpliedVolatility(D24,D26)</f>
+        <v>0.4</v>
+      </c>
+      <c r="E27" s="2">
+        <f t="array" ref="E27">_xll.qlBlackCalibrationHelperImpliedVolatility(E24,E26)</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>31</v>
       </c>
-      <c r="B28" t="e" cm="1">
-        <f t="array" aca="1" ref="B28" ca="1">_xll.qlBlackCalibrationHelperBlackPrice(B24,B27)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C28" t="e" cm="1">
-        <f t="array" aca="1" ref="C28" ca="1">_xll.qlBlackCalibrationHelperBlackPrice(C24,C27)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D28" t="e" cm="1">
-        <f t="array" aca="1" ref="D28" ca="1">_xll.qlBlackCalibrationHelperBlackPrice(D24,D27)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E28" t="e" cm="1">
-        <f t="array" aca="1" ref="E28" ca="1">_xll.qlBlackCalibrationHelperBlackPrice(E24,E27)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B28">
+        <f t="array" ref="B28">_xll.qlBlackCalibrationHelperBlackPrice(B24,B27)</f>
+        <v>9.1854188200250798E-3</v>
+      </c>
+      <c r="C28">
+        <f t="array" ref="C28">_xll.qlBlackCalibrationHelperBlackPrice(C24,C27)</f>
+        <v>0.5687196556581241</v>
+      </c>
+      <c r="D28">
+        <f t="array" ref="D28">_xll.qlBlackCalibrationHelperBlackPrice(D24,D27)</f>
+        <v>9.1854188200250798E-3</v>
+      </c>
+      <c r="E28">
+        <f t="array" ref="E28">_xll.qlBlackCalibrationHelperBlackPrice(E24,E27)</f>
+        <v>9.1360994073147565E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B29" ca="1">_xll.qlBlackCalibrationHelperVolatility(B24)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C29" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="C29" ca="1">_xll.qlBlackCalibrationHelperVolatility(C24)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D29" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="D29" ca="1">_xll.qlBlackCalibrationHelperVolatility(D24)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E29" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="E29" ca="1">_xll.qlBlackCalibrationHelperVolatility(E24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B29" s="1">
+        <f t="array" ref="B29">_xll.qlBlackCalibrationHelperVolatility(B24)</f>
+        <v>0.4</v>
+      </c>
+      <c r="C29" s="2">
+        <f t="array" ref="C29">_xll.qlBlackCalibrationHelperVolatility(C24)</f>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="D29" s="2">
+        <f t="array" ref="D29">_xll.qlBlackCalibrationHelperVolatility(D24)</f>
+        <v>0.4</v>
+      </c>
+      <c r="E29" s="2">
+        <f t="array" ref="E29">_xll.qlBlackCalibrationHelperVolatility(E24)</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>33</v>
       </c>
-      <c r="B30" t="e" cm="1">
-        <f t="array" aca="1" ref="B30" ca="1">_xll.qlBlackCalibrationHelperVolatilityType(B24)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C30" t="e" cm="1">
-        <f t="array" aca="1" ref="C30" ca="1">_xll.qlBlackCalibrationHelperVolatilityType(C24)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D30" t="e" cm="1">
-        <f t="array" aca="1" ref="D30" ca="1">_xll.qlBlackCalibrationHelperVolatilityType(D24)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E30" t="e" cm="1">
-        <f t="array" aca="1" ref="E30" ca="1">_xll.qlBlackCalibrationHelperVolatilityType(E24)</f>
-        <v>#VALUE!</v>
+      <c r="B30" t="str">
+        <f t="array" ref="B30">_xll.qlBlackCalibrationHelperVolatilityType(B24)</f>
+        <v>SHIFTEDLOGNORMAL</v>
+      </c>
+      <c r="C30" t="str">
+        <f t="array" ref="C30">_xll.qlBlackCalibrationHelperVolatilityType(C24)</f>
+        <v>NORMAL</v>
+      </c>
+      <c r="D30" t="str">
+        <f t="array" ref="D30">_xll.qlBlackCalibrationHelperVolatilityType(D24)</f>
+        <v>SHIFTEDLOGNORMAL</v>
+      </c>
+      <c r="E30" t="str">
+        <f t="array" ref="E30">_xll.qlBlackCalibrationHelperVolatilityType(E24)</f>
+        <v>SHIFTEDLOGNORMAL</v>
       </c>
     </row>
   </sheetData>
@@ -1031,14 +1020,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C28359EE-9D7F-4D21-9C31-A047A51C0E20}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="37.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5546875" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="37.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5" customWidth="1"/>
+    <col min="3" max="3" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -1046,34 +1035,34 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B2" ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" cm="1">
+        <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="e" cm="1">
-        <f t="array" aca="1" ref="B4" ca="1">_xll.qlFlatForward(B2,0.03)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" t="str">
+        <f>_xll.qlFlatForward(B2,0.03,"actual365fixed")</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlCapHelper!R4C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" t="e" cm="1">
-        <f t="array" aca="1" ref="B5" ca="1">_xll.qlFlatForward(B2,0.02)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5" t="str">
+        <f>_xll.qlFlatForward(B2,0.02,"actual365fixed")</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlCapHelper!R5C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="B7" s="9" t="s">
         <v>39</v>
       </c>
@@ -1081,7 +1070,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -1104,7 +1093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1127,17 +1116,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B10" ca="1">_xll.qlEuribor("6m",$B$4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C10" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_xll.qlEuribor("6m",$B$4)</f>
-        <v>#VALUE!</v>
+      <c r="B10" s="4" t="str" cm="1">
+        <f t="array" ref="B10">_xll.qlEuribor("6m",$B$4)</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlCapHelper!R10C2Euribor,A</v>
+      </c>
+      <c r="C10" s="4" t="str" cm="1">
+        <f t="array" ref="C10">_xll.qlEuribor("6m",$B$4)</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlCapHelper!R10C3Euribor,A</v>
       </c>
       <c r="D10" t="s">
         <v>1</v>
@@ -1152,7 +1141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -1175,7 +1164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1198,7 +1187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -1221,17 +1210,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="4" t="e">
-        <f ca="1">$B$5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C14" s="4" t="e">
-        <f ca="1">$B$5</f>
-        <v>#VALUE!</v>
+      <c r="B14" s="4" t="str">
+        <f>$B$5</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlCapHelper!R5C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C14" s="4" t="str">
+        <f>$B$5</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlCapHelper!R5C2YieldTermStructureHandle,A</v>
       </c>
       <c r="D14" t="s">
         <v>1</v>
@@ -1246,7 +1235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1267,7 +1256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -1288,7 +1277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1309,79 +1298,79 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B19" t="e" cm="1">
-        <f t="array" aca="1" ref="B19" ca="1">_xll.qlCapHelper(B8,B9,B10,B11,B12,B13,B14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C19" t="e" cm="1">
-        <f t="array" aca="1" ref="C19" ca="1">_xll.qlCapHelper(C8,C9,C10,C11,C12,C13,C14,C15,C16,C17)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
+      <c r="B19" t="str" cm="1">
+        <f t="array" ref="B19">_xll.qlCapHelper(B8,B9,B10,B11,B12,B13,B14)</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlCapHelper!R19C2CapHelper,A</v>
+      </c>
+      <c r="C19" t="str" cm="1">
+        <f t="array" ref="C19">_xll.qlCapHelper(C8,C9,C10,C11,C12,C13,C14,C15,C16,C17)</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlCapHelper!R19C3CapHelper,A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21" t="e" cm="1">
-        <f t="array" aca="1" ref="B21" ca="1">_xll.qlBlackCalibrationHelperMarketValue(B19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C21" t="e" cm="1">
-        <f t="array" aca="1" ref="C21" ca="1">_xll.qlBlackCalibrationHelperMarketValue(C19)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B21" cm="1">
+        <f t="array" ref="B21">_xll.qlBlackCalibrationHelperMarketValue(B19)</f>
+        <v>2.5622813960893911E-2</v>
+      </c>
+      <c r="C21" cm="1">
+        <f t="array" ref="C21">_xll.qlBlackCalibrationHelperMarketValue(C19)</f>
+        <v>1.9464920445835268E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B22" ca="1">_xll.qlBlackCalibrationHelperImpliedVolatility(B19,B21)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C22" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="C22" ca="1">_xll.qlBlackCalibrationHelperImpliedVolatility(C19,C21)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="1" cm="1">
+        <f t="array" ref="B22">_xll.qlBlackCalibrationHelperImpliedVolatility(B19,B21)</f>
+        <v>0.35</v>
+      </c>
+      <c r="C22" s="1" cm="1">
+        <f t="array" ref="C22">_xll.qlBlackCalibrationHelperImpliedVolatility(C19,C21)</f>
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" t="e" cm="1">
-        <f t="array" aca="1" ref="B23" ca="1">_xll.qlBlackCalibrationHelperBlackPrice(B19,B22)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C23" t="e" cm="1">
-        <f t="array" aca="1" ref="C23" ca="1">_xll.qlBlackCalibrationHelperBlackPrice(C19,C22)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B23" cm="1">
+        <f t="array" ref="B23">_xll.qlBlackCalibrationHelperBlackPrice(B19,B22)</f>
+        <v>2.5622813960893911E-2</v>
+      </c>
+      <c r="C23" cm="1">
+        <f t="array" ref="C23">_xll.qlBlackCalibrationHelperBlackPrice(C19,C22)</f>
+        <v>1.9464920445835268E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B24" ca="1">_xll.qlBlackCalibrationHelperVolatility(B19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C24" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="C24" ca="1">_xll.qlBlackCalibrationHelperVolatility(C19)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="1" cm="1">
+        <f t="array" ref="B24">_xll.qlBlackCalibrationHelperVolatility(B19)</f>
+        <v>0.35</v>
+      </c>
+      <c r="C24" s="1" cm="1">
+        <f t="array" ref="C24">_xll.qlBlackCalibrationHelperVolatility(C19)</f>
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B25" ca="1">_xll.qlBlackCalibrationHelperVolatilityType(B19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C25" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="C25" ca="1">_xll.qlBlackCalibrationHelperVolatilityType(C19)</f>
-        <v>#VALUE!</v>
+      <c r="B25" s="4" t="str" cm="1">
+        <f t="array" ref="B25">_xll.qlBlackCalibrationHelperVolatilityType(B19)</f>
+        <v>SHIFTEDLOGNORMAL</v>
+      </c>
+      <c r="C25" s="4" t="str" cm="1">
+        <f t="array" ref="C25">_xll.qlBlackCalibrationHelperVolatilityType(C19)</f>
+        <v>NORMAL</v>
       </c>
     </row>
   </sheetData>
@@ -1392,14 +1381,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2915A64-63DC-4465-A37C-0C1DB7EAA7FC}">
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="37.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="20.5546875" customWidth="1"/>
+    <col min="3" max="3" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -1407,34 +1396,34 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B2" ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" cm="1">
+        <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" t="e" cm="1">
-        <f t="array" aca="1" ref="B4" ca="1">_xll.qlFlatForward(B2,0.03)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" t="str">
+        <f>_xll.qlFlatForward(B2,0.03,"actual365fixed")</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlHestonModelHelper!R4C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>48</v>
       </c>
-      <c r="B5" t="e" cm="1">
-        <f t="array" aca="1" ref="B5" ca="1">_xll.qlFlatForward(B2,0.02)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" t="str">
+        <f>_xll.qlFlatForward(B2,0.02,"actual365fixed")</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlHestonModelHelper!R5C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="B7" t="s">
         <v>49</v>
       </c>
@@ -1442,7 +1431,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -1465,7 +1454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -1488,7 +1477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -1511,7 +1500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -1534,7 +1523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1557,17 +1546,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>44</v>
       </c>
-      <c r="B13" t="e">
-        <f ca="1">$B$4</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C13" t="e">
-        <f ca="1">$B$4</f>
-        <v>#VALUE!</v>
+      <c r="B13" t="str">
+        <f>$B$4</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlHestonModelHelper!R4C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C13" t="str">
+        <f>$B$4</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlHestonModelHelper!R4C2YieldTermStructureHandle,A</v>
       </c>
       <c r="E13" t="s">
         <v>1</v>
@@ -1582,17 +1571,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>45</v>
       </c>
-      <c r="B14" t="e">
-        <f ca="1">$B$5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C14" t="e">
-        <f ca="1">$B$5</f>
-        <v>#VALUE!</v>
+      <c r="B14" t="str">
+        <f>$B$5</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlHestonModelHelper!R5C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C14" t="str">
+        <f>$B$5</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlHestonModelHelper!R5C2YieldTermStructureHandle,A</v>
       </c>
       <c r="E14" t="s">
         <v>1</v>
@@ -1607,7 +1596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1627,79 +1616,79 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B17" t="e" cm="1">
-        <f t="array" aca="1" ref="B17" ca="1">_xll.qlHestonModelHelper(B8,B9,B10,B11,B12,B13,B14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C17" t="e" cm="1">
-        <f t="array" aca="1" ref="C17" ca="1">_xll.qlHestonModelHelper(C8,C9,C10,C11,C12,C13,C14,C15)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
+      <c r="B17" t="str" cm="1">
+        <f t="array" ref="B17">_xll.qlHestonModelHelper(B8,B9,B10,B11,B12,B13,B14)</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlHestonModelHelper!R17C2HestonModelHelper,A</v>
+      </c>
+      <c r="C17" t="str" cm="1">
+        <f t="array" ref="C17">_xll.qlHestonModelHelper(C8,C9,C10,C11,C12,C13,C14,C15)</f>
+        <v>欣[test_calibrationhelpers.xlsx]qlHestonModelHelper!R17C3HestonModelHelper,A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>29</v>
       </c>
-      <c r="B19" t="e" cm="1">
-        <f t="array" aca="1" ref="B19" ca="1">_xll.qlBlackCalibrationHelperMarketValue(B17)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C19" t="e" cm="1">
-        <f t="array" aca="1" ref="C19" ca="1">_xll.qlBlackCalibrationHelperMarketValue(C17)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B19" cm="1">
+        <f t="array" ref="B19">_xll.qlBlackCalibrationHelperMarketValue(B17)</f>
+        <v>12.424776089141019</v>
+      </c>
+      <c r="C19" cm="1">
+        <f t="array" ref="C19">_xll.qlBlackCalibrationHelperMarketValue(C17)</f>
+        <v>12.424776089141019</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B20" ca="1">_xll.qlBlackCalibrationHelperImpliedVolatility(B17,B19)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C20" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="C20" ca="1">_xll.qlBlackCalibrationHelperImpliedVolatility(C17,C19)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" cm="1">
+        <f t="array" ref="B20">_xll.qlBlackCalibrationHelperImpliedVolatility(B17,B19)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C20" s="1" cm="1">
+        <f t="array" ref="C20">_xll.qlBlackCalibrationHelperImpliedVolatility(C17,C19)</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>31</v>
       </c>
-      <c r="B21" t="e" cm="1">
-        <f t="array" aca="1" ref="B21" ca="1">_xll.qlBlackCalibrationHelperBlackPrice(B17,B20)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C21" t="e" cm="1">
-        <f t="array" aca="1" ref="C21" ca="1">_xll.qlBlackCalibrationHelperBlackPrice(C17,C20)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B21" cm="1">
+        <f t="array" ref="B21">_xll.qlBlackCalibrationHelperBlackPrice(B17,B20)</f>
+        <v>12.424776089141019</v>
+      </c>
+      <c r="C21" cm="1">
+        <f t="array" ref="C21">_xll.qlBlackCalibrationHelperBlackPrice(C17,C20)</f>
+        <v>12.424776089141019</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B22" ca="1">_xll.qlBlackCalibrationHelperVolatility(B17)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C22" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="C22" ca="1">_xll.qlBlackCalibrationHelperVolatility(C17)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B22" s="1" cm="1">
+        <f t="array" ref="B22">_xll.qlBlackCalibrationHelperVolatility(B17)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C22" s="1" cm="1">
+        <f t="array" ref="C22">_xll.qlBlackCalibrationHelperVolatility(C17)</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B23" ca="1">_xll.qlBlackCalibrationHelperVolatilityType(B17)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C23" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="C23" ca="1">_xll.qlBlackCalibrationHelperVolatilityType(C17)</f>
-        <v>#VALUE!</v>
+      <c r="B23" s="4" t="str" cm="1">
+        <f t="array" ref="B23">_xll.qlBlackCalibrationHelperVolatilityType(B17)</f>
+        <v>SHIFTEDLOGNORMAL</v>
+      </c>
+      <c r="C23" s="4" t="str" cm="1">
+        <f t="array" ref="C23">_xll.qlBlackCalibrationHelperVolatilityType(C17)</f>
+        <v>SHIFTEDLOGNORMAL</v>
       </c>
     </row>
   </sheetData>
